--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488281_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488281_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>J. REMESAL LEON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6512</v>
+        <v>4.615</v>
       </c>
       <c r="E2" t="n">
-        <v>3.783</v>
+        <v>3.7223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8682</v>
+        <v>0.8927</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9008</v>
+        <v>1.556</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4846</v>
+        <v>0.2182</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4162</v>
+        <v>1.3378</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5357</v>
+        <v>3.0926</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0736</v>
+        <v>1.6399</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4622</v>
+        <v>1.4527</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.635</v>
+        <v>-1.5367</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.589</v>
+        <v>-1.4217</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.046</v>
+        <v>-0.115</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1853</v>
+        <v>-5.0027</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1117</v>
+        <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>1.824</v>
+        <v>-0.5677</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4326</v>
+        <v>-0.3463</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3914</v>
+        <v>-0.2214</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.6648</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>5.9787</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. REMESAL LEON</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3967</v>
+        <v>3.4011</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1347</v>
+        <v>2.8037</v>
       </c>
       <c r="F3" t="n">
-        <v>1.262</v>
+        <v>0.5974</v>
       </c>
       <c r="G3" t="n">
-        <v>1.556</v>
+        <v>1.9008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2182</v>
+        <v>0.4846</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3378</v>
+        <v>1.4162</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0926</v>
+        <v>2.5357</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6399</v>
+        <v>1.0736</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4527</v>
+        <v>1.4622</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5367</v>
+        <v>-0.635</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4217</v>
+        <v>-0.589</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.115</v>
+        <v>-0.046</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.0027</v>
+        <v>-0.1853</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9646</v>
+        <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7859</v>
+        <v>0.5739</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9339</v>
+        <v>0.4533</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1479</v>
+        <v>0.1206</v>
       </c>
       <c r="V3" t="n">
-        <v>5.6648</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5.9787</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6856</v>
+        <v>0.877</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0476</v>
+        <v>1.3621</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.362</v>
+        <v>-0.4851</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4949</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8655</v>
+        <v>0.0569</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8643</v>
+        <v>0.1788</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0012</v>
+        <v>-0.1219</v>
       </c>
       <c r="V5" t="n">
         <v>0.9444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4299</v>
+        <v>-0.0617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2883</v>
+        <v>0.4842</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0.3941</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1025</v>
+        <v>0.4707</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4004</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.298</v>
+        <v>-0.1256</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.983</v>
+        <v>-1.1044</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2529</v>
+        <v>-0.0408</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2359</v>
+        <v>-1.0636</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5004</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.907</v>
+        <v>0.7856</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8891</v>
+        <v>0.5954</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0179</v>
+        <v>0.1903</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9455</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7649</v>
+        <v>-2.4225</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5414</v>
+        <v>-0.1497</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2235</v>
+        <v>-2.2728</v>
       </c>
       <c r="G10" t="n">
         <v>4.2595</v>
@@ -1234,13 +1234,13 @@
         <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0985</v>
+        <v>-0.7561</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.4626</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2443</v>
+        <v>-0.2935</v>
       </c>
       <c r="V10" t="n">
         <v>-3.1466</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.546</v>
+        <v>-2.6959</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3996</v>
+        <v>-2.1146</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9456</v>
+        <v>-0.5813</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3135</v>
+        <v>-3.3126</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-2.2882</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4853</v>
+        <v>-1.0245</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0808</v>
+        <v>-1.5061</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4891</v>
+        <v>-0.9883</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5699</v>
+        <v>-0.5178</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2327</v>
+        <v>-1.8065</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3173</v>
+        <v>-1.2998</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.5067</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1117</v>
+        <v>-1.297</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4143</v>
+        <v>-0.18</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7039</v>
+        <v>0.3746</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2895</v>
+        <v>-0.5546</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8321</v>
+        <v>-0.315</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8883</v>
+        <v>0.3139</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.7204</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7261</v>
+        <v>-4.1341</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8001</v>
+        <v>0.91</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.926</v>
+        <v>-5.0441</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3126</v>
+        <v>-1.3135</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2882</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0245</v>
+        <v>-0.4853</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5061</v>
+        <v>-0.0808</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9883</v>
+        <v>0.4891</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5178</v>
+        <v>-0.5699</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8065</v>
+        <v>-1.2327</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2998</v>
+        <v>-1.3173</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5067</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.297</v>
+        <v>-1.1117</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2102</v>
+        <v>-0.1738</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3109</v>
+        <v>0.2142</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8993</v>
+        <v>-0.388</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.315</v>
+        <v>-2.8321</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3139</v>
+        <v>1.8883</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6289</v>
+        <v>-4.7204</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1065</v>
+        <v>-4.2974</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2235</v>
+        <v>-1.6359</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8831</v>
+        <v>-2.6615</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9963</v>
@@ -1468,13 +1468,13 @@
         <v>2.9646</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9451</v>
+        <v>-1.136</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2584</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6867</v>
+        <v>-0.4651</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8327</v>
@@ -1504,10 +1504,10 @@
         <v>-2.968399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>8.195600000000001</v>
+        <v>8.195800000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.1641</v>
+        <v>-11.1642</v>
       </c>
       <c r="G14" t="n">
         <v>2.347200000000001</v>
@@ -1531,7 +1531,7 @@
         <v>-10.5983</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.6027</v>
+        <v>-8.602699999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-1.9958</v>
@@ -1546,13 +1546,13 @@
         <v>14.823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9264000000000001</v>
+        <v>-0.9265</v>
       </c>
       <c r="T14" t="n">
         <v>0.9327999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8594</v>
+        <v>-1.8592</v>
       </c>
       <c r="V14" t="n">
         <v>-3.4627</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.569699999999999</v>
+        <v>6.3392</v>
       </c>
       <c r="E15" t="n">
-        <v>8.1951</v>
+        <v>6.4324</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3746</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>3.5401</v>
@@ -1624,13 +1624,13 @@
         <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>3.992</v>
+        <v>1.7615</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8987</v>
+        <v>1.136</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0933</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.63</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2608</v>
+        <v>2.3142</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7953</v>
+        <v>4.3829</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5345</v>
+        <v>-2.0687</v>
       </c>
       <c r="G16" t="n">
         <v>2.7075</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2171</v>
+        <v>0.2705</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7449</v>
+        <v>-0.1573</v>
       </c>
       <c r="U16" t="n">
-        <v>0.962</v>
+        <v>0.4278</v>
       </c>
       <c r="V16" t="n">
         <v>-2.5166</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6643</v>
+        <v>1.6889</v>
       </c>
       <c r="E17" t="n">
         <v>1.2309</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4334</v>
+        <v>0.458</v>
       </c>
       <c r="G17" t="n">
         <v>1.332</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0383</v>
+        <v>-0.0137</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3221</v>
+        <v>0.5256</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3221</v>
+        <v>0.7217</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.1962</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3221</v>
+        <v>-3.3955</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>-2.059</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.3365</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3221</v>
+        <v>-1.2965</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>-1.3191</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.0989</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.7398</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.3591</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.2643</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1126</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.3768</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6673</v>
+        <v>0.3221</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.764</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3216</v>
+        <v>0.3221</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2432</v>
+        <v>0.3221</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9101</v>
+        <v>0.3221</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7857</v>
+        <v>0.3221</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5885</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5426</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.046</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3447</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8133</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1218</v>
+        <v>0.2699</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4422</v>
+        <v>-1.0505</v>
       </c>
       <c r="F20" t="n">
         <v>1.3205</v>
@@ -2014,10 +2014,10 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0423</v>
+        <v>0.3494</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>0.0634</v>
       </c>
       <c r="U20" t="n">
         <v>0.286</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4142</v>
+        <v>0.2317</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1342</v>
+        <v>1.6394</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5484</v>
+        <v>-1.4077</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3955</v>
+        <v>-0.8875</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.059</v>
+        <v>-2.1501</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3365</v>
+        <v>1.2626</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2965</v>
+        <v>2.0556</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3191</v>
+        <v>-1.242</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0226</v>
+        <v>3.2976</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0989</v>
+        <v>-2.9431</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7398</v>
+        <v>-0.9081</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3591</v>
+        <v>-2.035</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6676</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-6.485</v>
       </c>
       <c r="R21" t="n">
-        <v>2.594</v>
+        <v>2.9646</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.204</v>
+        <v>-0.0808</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.475</v>
+        <v>0.0896</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.729</v>
+        <v>-0.1704</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5177</v>
+        <v>4.7204</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8321</v>
+        <v>5.9793</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.862</v>
+        <v>-0.528</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8947</v>
+        <v>1.8839</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0327</v>
+        <v>-2.4118</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5388</v>
+        <v>0.3216</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7048</v>
+        <v>0.2432</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8339</v>
+        <v>0.0784</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7755</v>
+        <v>0.9101</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.817</v>
+        <v>0.7857</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>0.1244</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7633</v>
+        <v>-0.5885</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8878</v>
+        <v>-0.5426</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8754</v>
+        <v>-0.046</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5847</v>
+        <v>-0.776</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1604</v>
+        <v>0.0299</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4243</v>
+        <v>-0.8058</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8332</v>
+        <v>-0.6294</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5733</v>
+        <v>0.9439</v>
       </c>
       <c r="X22" t="n">
-        <v>1.26</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1994</v>
+        <v>-0.9691</v>
       </c>
       <c r="E23" t="n">
-        <v>0.856</v>
+        <v>0.1719</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0554</v>
+        <v>-1.141</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8875</v>
+        <v>-0.5463</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1501</v>
+        <v>0.2002</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2626</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0556</v>
+        <v>-0.0419</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.242</v>
+        <v>0.5281</v>
       </c>
       <c r="L23" t="n">
-        <v>3.2976</v>
+        <v>-0.5699</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9431</v>
+        <v>-0.5044</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9081</v>
+        <v>-0.3278</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.035</v>
+        <v>-0.1766</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.5205</v>
+        <v>0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.485</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.9646</v>
+        <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5119</v>
+        <v>-0.4054</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6939</v>
+        <v>-0.1007</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.3047</v>
       </c>
       <c r="V23" t="n">
-        <v>4.7204</v>
+        <v>-0.9439</v>
       </c>
       <c r="W23" t="n">
-        <v>5.9793</v>
+        <v>0.3144</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6145</v>
+        <v>-1.0836</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2199</v>
+        <v>-1.8947</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3946</v>
+        <v>0.8111</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5463</v>
+        <v>-3.5388</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2002</v>
+        <v>-2.7048</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.8339</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0419</v>
+        <v>-1.7755</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5281</v>
+        <v>-1.817</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5699</v>
+        <v>0.0415</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5044</v>
+        <v>-1.7633</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3278</v>
+        <v>-0.8878</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1766</v>
+        <v>-0.8754</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9264</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0508</v>
+        <v>0.3631</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4924</v>
+        <v>0.1604</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5584</v>
+        <v>0.2027</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9439</v>
+        <v>2.8332</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2583</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.54</v>
+        <v>-5.4897</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4798</v>
+        <v>-2.6756</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0602</v>
+        <v>-2.814</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3817</v>
@@ -2404,13 +2404,13 @@
         <v>2.0382</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3246</v>
+        <v>0.3749</v>
       </c>
       <c r="T25" t="n">
-        <v>0.776</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4514</v>
+        <v>-0.2052</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8888</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.968299999999998</v>
+        <v>3.621199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>11.1643</v>
+        <v>11.1644</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.1959</v>
+        <v>-7.543</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.347200000000001</v>
+        <v>-2.3472</v>
       </c>
       <c r="H26" t="n">
         <v>3.8736</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.2206</v>
+        <v>-6.220599999999999</v>
       </c>
       <c r="J26" t="n">
         <v>10.5982</v>
       </c>
       <c r="K26" t="n">
-        <v>8.602600000000002</v>
+        <v>8.602599999999999</v>
       </c>
       <c r="L26" t="n">
         <v>1.9956</v>
@@ -2470,10 +2470,10 @@
         <v>-4.729</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.216399999999998</v>
+        <v>-8.2164</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9265000000000003</v>
+        <v>0.9264999999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.8229</v>
@@ -2482,16 +2482,16 @@
         <v>15.7494</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9263999999999999</v>
+        <v>1.5792</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8592</v>
+        <v>1.8593</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9328</v>
+        <v>-0.2799000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>3.462600000000001</v>
+        <v>3.4626</v>
       </c>
       <c r="W26" t="n">
         <v>13.5296</v>
